--- a/UiPath_Invoice_Tracker_Template.xlsx
+++ b/UiPath_Invoice_Tracker_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raunaq.M\Documents\UiPath\pdfToExcel\Output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE4EF0E-13EC-4CF3-941F-BADB0636D875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA65951-1EDF-4CBF-9DE0-6F3F8FE3D52A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="345" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice Register" sheetId="1" r:id="rId1"/>
